--- a/research/traditional_assets/database/data/finland/finland_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.118</v>
+        <v>0.073175</v>
       </c>
       <c r="E2">
-        <v>0.279</v>
+        <v>0.104</v>
       </c>
       <c r="F2">
-        <v>0.6520000000000001</v>
+        <v>0.158</v>
       </c>
       <c r="G2">
-        <v>0.2083551430232578</v>
+        <v>0.4730197880370492</v>
       </c>
       <c r="H2">
-        <v>0.2055248562265457</v>
+        <v>0.4730197880370492</v>
       </c>
       <c r="I2">
-        <v>0.2797135337856474</v>
+        <v>0.285758290032094</v>
       </c>
       <c r="J2">
-        <v>0.2389786778374505</v>
+        <v>0.251815903618762</v>
       </c>
       <c r="K2">
-        <v>322.28</v>
+        <v>133.773</v>
       </c>
       <c r="L2">
-        <v>0.549484836653237</v>
+        <v>0.2691241439803005</v>
       </c>
       <c r="M2">
-        <v>123.5936</v>
+        <v>186.735</v>
       </c>
       <c r="N2">
-        <v>0.03118475400363841</v>
+        <v>0.06657432858808304</v>
       </c>
       <c r="O2">
-        <v>0.3834975797443216</v>
+        <v>1.395909488461797</v>
       </c>
       <c r="P2">
-        <v>103.8536</v>
+        <v>185.344</v>
       </c>
       <c r="Q2">
-        <v>0.02620401839894834</v>
+        <v>0.06607841249808372</v>
       </c>
       <c r="R2">
-        <v>0.3222464937321584</v>
+        <v>1.385511276565525</v>
       </c>
       <c r="S2">
-        <v>19.74</v>
+        <v>1.390999999999999</v>
       </c>
       <c r="T2">
-        <v>0.1597170080004142</v>
+        <v>0.007449058826679514</v>
       </c>
       <c r="U2">
-        <v>106.891</v>
+        <v>79.89500000000001</v>
       </c>
       <c r="V2">
-        <v>0.02697040575080678</v>
+        <v>0.02848397987814226</v>
       </c>
       <c r="W2">
-        <v>0.3714285714285714</v>
+        <v>0.1699499249002099</v>
       </c>
       <c r="X2">
-        <v>0.04907671415549</v>
+        <v>0.08159013923680669</v>
       </c>
       <c r="Y2">
-        <v>0.3223518572730815</v>
+        <v>0.08835978566340316</v>
       </c>
       <c r="Z2">
-        <v>0.8129789529952804</v>
+        <v>0.6795294878988057</v>
       </c>
       <c r="AA2">
-        <v>0.08032692466795222</v>
+        <v>0.08409154752755596</v>
       </c>
       <c r="AB2">
-        <v>0.04669657199083718</v>
+        <v>0.07636713008016621</v>
       </c>
       <c r="AC2">
-        <v>0.03363638929344057</v>
+        <v>0.008187858509256879</v>
       </c>
       <c r="AD2">
-        <v>313.02</v>
+        <v>386.55</v>
       </c>
       <c r="AE2">
-        <v>0.04188079389296499</v>
+        <v>0.008491451635729707</v>
       </c>
       <c r="AF2">
-        <v>313.061880793893</v>
+        <v>386.5584914516357</v>
       </c>
       <c r="AG2">
-        <v>206.1708807938929</v>
+        <v>306.6634914516358</v>
       </c>
       <c r="AH2">
-        <v>0.07320804126544397</v>
+        <v>0.1211224527163701</v>
       </c>
       <c r="AI2">
-        <v>0.2365655874915222</v>
+        <v>0.3473314063811712</v>
       </c>
       <c r="AJ2">
-        <v>0.04944808829011061</v>
+        <v>0.09855576038751016</v>
       </c>
       <c r="AK2">
-        <v>0.1694827916138377</v>
+        <v>0.2968543860827305</v>
       </c>
       <c r="AL2">
-        <v>11.98</v>
+        <v>13.372</v>
       </c>
       <c r="AM2">
-        <v>8.774000000000001</v>
+        <v>11.834</v>
       </c>
       <c r="AN2">
-        <v>1.765522064795596</v>
+        <v>2.237030949790505</v>
       </c>
       <c r="AO2">
-        <v>13.69123539232053</v>
+        <v>10.62174693389171</v>
       </c>
       <c r="AP2">
-        <v>1.162862562008691</v>
+        <v>1.774714064281788</v>
       </c>
       <c r="AQ2">
-        <v>18.69398222019603</v>
+        <v>12.0021970593206</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Taaleri Oyj (HLSE:TAALA)</t>
+          <t>Evli Oyj (HLSE:EVLI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,53 +724,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.08259999999999999</v>
-      </c>
-      <c r="E3">
-        <v>0.5679999999999999</v>
-      </c>
       <c r="G3">
-        <v>0.2450331125827814</v>
+        <v>0.6321393998063891</v>
       </c>
       <c r="H3">
-        <v>0.2450331125827814</v>
+        <v>0.6321393998063891</v>
       </c>
       <c r="I3">
-        <v>0.3746452223273415</v>
+        <v>0.4114230396902226</v>
       </c>
       <c r="J3">
-        <v>0.3031323956946453</v>
+        <v>0.3268854008205412</v>
       </c>
       <c r="K3">
-        <v>151.8</v>
+        <v>28.9</v>
       </c>
       <c r="L3">
-        <v>1.436140018921476</v>
+        <v>0.2797676669893514</v>
       </c>
       <c r="M3">
-        <v>30.2</v>
+        <v>42.684</v>
       </c>
       <c r="N3">
-        <v>0.08414600167177487</v>
+        <v>0.1003385049365303</v>
       </c>
       <c r="O3">
-        <v>0.1989459815546772</v>
+        <v>1.476955017301038</v>
       </c>
       <c r="P3">
-        <v>10.5</v>
+        <v>41.9</v>
       </c>
       <c r="Q3">
-        <v>0.02925606018389524</v>
+        <v>0.09849553361542078</v>
       </c>
       <c r="R3">
-        <v>0.06916996047430829</v>
+        <v>1.449826989619377</v>
       </c>
       <c r="S3">
-        <v>19.7</v>
+        <v>0.7839999999999989</v>
       </c>
       <c r="T3">
-        <v>0.652317880794702</v>
+        <v>0.01836753818761126</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -779,52 +773,52 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.04790808299099488</v>
+        <v>0.08396189941187253</v>
       </c>
       <c r="AB3">
-        <v>0.04669483619627176</v>
+        <v>0.0773127357958221</v>
       </c>
       <c r="AD3">
-        <v>17.2</v>
+        <v>107.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.2</v>
+        <v>107.3</v>
       </c>
       <c r="AG3">
-        <v>17.2</v>
+        <v>107.3</v>
       </c>
       <c r="AH3">
-        <v>0.04573251794735443</v>
+        <v>0.2014266941993618</v>
       </c>
       <c r="AI3">
-        <v>0.06321205439176772</v>
+        <v>0.5208737864077669</v>
       </c>
       <c r="AJ3">
-        <v>0.04573251794735443</v>
+        <v>0.2014266941993618</v>
       </c>
       <c r="AK3">
-        <v>0.06321205439176772</v>
+        <v>0.5208737864077669</v>
       </c>
       <c r="AL3">
-        <v>3.46</v>
+        <v>0.981</v>
       </c>
       <c r="AM3">
-        <v>3.46</v>
+        <v>0.981</v>
       </c>
       <c r="AN3">
-        <v>0.4310776942355889</v>
+        <v>2.495348837209302</v>
       </c>
       <c r="AO3">
-        <v>11.44508670520231</v>
+        <v>43.32313965341488</v>
       </c>
       <c r="AP3">
-        <v>0.4310776942355889</v>
+        <v>2.495348837209302</v>
       </c>
       <c r="AQ3">
-        <v>11.44508670520231</v>
+        <v>43.32313965341488</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alexandria Pankkiiriliike Oyj (HLSE:ALEX)</t>
+          <t>Titanium Oyj (HLSE:TITAN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -843,41 +837,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.244</v>
+      </c>
+      <c r="E4">
+        <v>0.303</v>
+      </c>
       <c r="G4">
-        <v>0.1847250509164969</v>
+        <v>0.644927536231884</v>
       </c>
       <c r="H4">
-        <v>0.1847250509164969</v>
+        <v>0.644927536231884</v>
       </c>
       <c r="I4">
-        <v>0.219959266802444</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="J4">
-        <v>0.1815177874640729</v>
+        <v>0.4703188405797101</v>
       </c>
       <c r="K4">
-        <v>7.45</v>
+        <v>11.6</v>
       </c>
       <c r="L4">
-        <v>0.1517311608961303</v>
+        <v>0.4202898550724637</v>
       </c>
       <c r="M4">
-        <v>5.98</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N4">
-        <v>0.0659316427783903</v>
+        <v>0.05700879765395895</v>
       </c>
       <c r="O4">
-        <v>0.8026845637583893</v>
+        <v>0.8379310344827587</v>
       </c>
       <c r="P4">
-        <v>5.98</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="Q4">
-        <v>0.0659316427783903</v>
+        <v>0.05700879765395895</v>
       </c>
       <c r="R4">
-        <v>0.8026845637583893</v>
+        <v>0.8379310344827587</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,58 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>13.4</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>0.07859237536656892</v>
+      </c>
+      <c r="W4">
+        <v>0.5272727272727272</v>
       </c>
       <c r="X4">
-        <v>0.04907671415549</v>
+        <v>0.07659232036578076</v>
+      </c>
+      <c r="Y4">
+        <v>0.4506804069069464</v>
+      </c>
+      <c r="Z4">
+        <v>4.276417725441586</v>
+      </c>
+      <c r="AA4">
+        <v>2.011279826464208</v>
       </c>
       <c r="AB4">
-        <v>0.04722085719759266</v>
+        <v>0.07634680571615854</v>
+      </c>
+      <c r="AC4">
+        <v>1.934933020748049</v>
       </c>
       <c r="AD4">
-        <v>8.539999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>8.539999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="AG4">
-        <v>8.539999999999999</v>
+        <v>-12.19</v>
       </c>
       <c r="AH4">
-        <v>0.08605401047964528</v>
+        <v>0.007046764894298526</v>
       </c>
       <c r="AI4">
-        <v>0.2165314401622718</v>
+        <v>0.0530469092503288</v>
       </c>
       <c r="AJ4">
-        <v>0.08605401047964528</v>
+        <v>-0.07700082117364665</v>
       </c>
       <c r="AK4">
-        <v>0.2165314401622718</v>
+        <v>-1.295430393198725</v>
       </c>
       <c r="AL4">
-        <v>0.273</v>
+        <v>0.227</v>
       </c>
       <c r="AM4">
-        <v>0.273</v>
+        <v>0.162</v>
       </c>
       <c r="AN4">
-        <v>0.7116666666666666</v>
+        <v>0.06368421052631579</v>
       </c>
       <c r="AO4">
-        <v>39.56043956043956</v>
+        <v>74.00881057268722</v>
       </c>
       <c r="AP4">
-        <v>0.7116666666666666</v>
+        <v>-0.6415789473684211</v>
       </c>
       <c r="AQ4">
-        <v>39.56043956043956</v>
+        <v>103.7037037037037</v>
       </c>
     </row>
     <row r="5">
@@ -948,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Titanium Oyj (HLSE:TITAN)</t>
+          <t>eQ Oyj (HLSE:EQV1V)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -956,41 +971,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.188</v>
+      </c>
+      <c r="E5">
+        <v>0.253</v>
+      </c>
       <c r="G5">
-        <v>0.6910569105691057</v>
+        <v>0.6484560570071259</v>
       </c>
       <c r="H5">
-        <v>0.6910569105691057</v>
+        <v>0.6484560570071259</v>
       </c>
       <c r="I5">
-        <v>0.573170731707317</v>
+        <v>0.606975079687326</v>
       </c>
       <c r="J5">
-        <v>0.4378648540583767</v>
+        <v>0.4834419910621168</v>
       </c>
       <c r="K5">
-        <v>9.33</v>
+        <v>40.7</v>
       </c>
       <c r="L5">
-        <v>0.3792682926829268</v>
+        <v>0.4833729216152019</v>
       </c>
       <c r="M5">
-        <v>5.93</v>
+        <v>37.7</v>
       </c>
       <c r="N5">
-        <v>0.03421811886901327</v>
+        <v>0.03428519461622408</v>
       </c>
       <c r="O5">
-        <v>0.6355841371918542</v>
+        <v>0.9262899262899263</v>
       </c>
       <c r="P5">
-        <v>5.93</v>
+        <v>37.7</v>
       </c>
       <c r="Q5">
-        <v>0.03421811886901327</v>
+        <v>0.03428519461622408</v>
       </c>
       <c r="R5">
-        <v>0.6355841371918542</v>
+        <v>0.9262899262899263</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -999,73 +1020,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>11.1</v>
+        <v>0.027</v>
       </c>
       <c r="V5">
-        <v>0.06405077899596076</v>
+        <v>2.455438341214987e-05</v>
       </c>
       <c r="W5">
-        <v>0.4442857142857143</v>
+        <v>0.5030902348578492</v>
       </c>
       <c r="X5">
-        <v>0.04670018656202411</v>
+        <v>0.07653968735088998</v>
       </c>
       <c r="Y5">
-        <v>0.3975855277236902</v>
+        <v>0.4265505475069592</v>
       </c>
       <c r="Z5">
-        <v>5.015290519877677</v>
+        <v>1.020785577174739</v>
       </c>
       <c r="AA5">
-        <v>2.196019451546599</v>
+        <v>0.493490611876848</v>
       </c>
       <c r="AB5">
-        <v>0.04669668034754972</v>
+        <v>0.07638745444417389</v>
       </c>
       <c r="AC5">
-        <v>2.149322771199049</v>
+        <v>0.4171031574326741</v>
       </c>
       <c r="AD5">
-        <v>0.024</v>
+        <v>5.87</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.008491451635729707</v>
       </c>
       <c r="AF5">
-        <v>0.024</v>
+        <v>5.87849145163573</v>
       </c>
       <c r="AG5">
-        <v>-11.076</v>
+        <v>5.85149145163573</v>
       </c>
       <c r="AH5">
-        <v>0.0001384689944843184</v>
+        <v>0.005317599118474493</v>
       </c>
       <c r="AI5">
-        <v>0.001089720305121685</v>
+        <v>0.07259324477718444</v>
       </c>
       <c r="AJ5">
-        <v>-0.06827596409902356</v>
+        <v>0.005293304588111579</v>
       </c>
       <c r="AK5">
-        <v>-1.013914317099963</v>
+        <v>0.07228392394884645</v>
       </c>
       <c r="AL5">
-        <v>0.133</v>
+        <v>0.043</v>
       </c>
       <c r="AM5">
-        <v>-0.212</v>
+        <v>0.043</v>
       </c>
       <c r="AN5">
-        <v>0.001428571428571429</v>
+        <v>0.1139606670678911</v>
       </c>
       <c r="AO5">
-        <v>106.015037593985</v>
+        <v>1188.372093023256</v>
       </c>
       <c r="AP5">
-        <v>-0.6592857142857143</v>
+        <v>0.1136013405741857</v>
       </c>
       <c r="AQ5">
-        <v>-66.50943396226415</v>
+        <v>1188.372093023256</v>
       </c>
     </row>
     <row r="6">
@@ -1076,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eQ Oyj (HLSE:EQV1V)</t>
+          <t>Alexandria Pankkiiriliike Oyj (HLSE:ALEX)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1084,122 +1105,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.174</v>
-      </c>
-      <c r="E6">
-        <v>0.244</v>
-      </c>
       <c r="G6">
-        <v>0.4191419141914191</v>
+        <v>0.3174946004319654</v>
       </c>
       <c r="H6">
-        <v>0.4191419141914191</v>
+        <v>0.3174946004319654</v>
       </c>
       <c r="I6">
-        <v>0.5944403062840639</v>
+        <v>0.2354211663066955</v>
       </c>
       <c r="J6">
-        <v>0.4742288157739285</v>
+        <v>0.1913838399500336</v>
       </c>
       <c r="K6">
-        <v>43.1</v>
+        <v>7.35</v>
       </c>
       <c r="L6">
-        <v>0.4741474147414741</v>
+        <v>0.1587473002159827</v>
       </c>
       <c r="M6">
-        <v>28.9</v>
+        <v>7.987</v>
       </c>
       <c r="N6">
-        <v>0.02501081782778018</v>
+        <v>0.1152525252525253</v>
       </c>
       <c r="O6">
-        <v>0.6705336426914152</v>
+        <v>1.086666666666667</v>
       </c>
       <c r="P6">
-        <v>28.9</v>
+        <v>7.38</v>
       </c>
       <c r="Q6">
-        <v>0.02501081782778018</v>
+        <v>0.1064935064935065</v>
       </c>
       <c r="R6">
-        <v>0.6705336426914152</v>
+        <v>1.004081632653061</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>0.6070000000000002</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.07599849755853263</v>
       </c>
       <c r="U6">
-        <v>0.043</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>3.721332756382518e-05</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0.6338235294117647</v>
+        <v>0.2417763157894737</v>
       </c>
       <c r="X6">
-        <v>0.046733040721423</v>
+        <v>0.07914668967774546</v>
       </c>
       <c r="Y6">
-        <v>0.5870904886903416</v>
+        <v>0.1626296261117282</v>
       </c>
       <c r="Z6">
-        <v>1.286790297323961</v>
+        <v>1.584531143052704</v>
       </c>
       <c r="AA6">
-        <v>0.6102330388493231</v>
+        <v>0.3032536546778424</v>
       </c>
       <c r="AB6">
-        <v>0.04669662785920069</v>
+        <v>0.07599419324955703</v>
       </c>
       <c r="AC6">
-        <v>0.5635364109901224</v>
+        <v>0.2272594614282853</v>
       </c>
       <c r="AD6">
-        <v>1.62</v>
+        <v>6.38</v>
       </c>
       <c r="AE6">
-        <v>0.04188079389296499</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.661880793892965</v>
+        <v>6.38</v>
       </c>
       <c r="AG6">
-        <v>1.618880793892965</v>
+        <v>6.38</v>
       </c>
       <c r="AH6">
-        <v>0.001436169667767486</v>
+        <v>0.08430232558139536</v>
       </c>
       <c r="AI6">
-        <v>0.02012891152566734</v>
+        <v>0.1734638390429581</v>
       </c>
       <c r="AJ6">
-        <v>0.001399061773827647</v>
+        <v>0.08430232558139536</v>
       </c>
       <c r="AK6">
-        <v>0.01961830769295619</v>
+        <v>0.1734638390429581</v>
       </c>
       <c r="AL6">
-        <v>0.022</v>
+        <v>0.264</v>
       </c>
       <c r="AM6">
-        <v>0.022</v>
+        <v>0.264</v>
       </c>
       <c r="AN6">
-        <v>0.02975589148283526</v>
+        <v>0.5696428571428571</v>
       </c>
       <c r="AO6">
-        <v>2454.545454545455</v>
+        <v>41.28787878787879</v>
       </c>
       <c r="AP6">
-        <v>0.02973533409057115</v>
+        <v>0.5696428571428571</v>
       </c>
       <c r="AQ6">
-        <v>2454.545454545455</v>
+        <v>41.28787878787879</v>
       </c>
     </row>
     <row r="7">
@@ -1210,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sievi Capital Plc (HLSE:SIEVI)</t>
+          <t>CapMan Oyj (HLSE:CAPMAN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1219,46 +1234,49 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.484</v>
+        <v>0.153</v>
       </c>
       <c r="E7">
-        <v>0.5</v>
+        <v>0.104</v>
+      </c>
+      <c r="F7">
+        <v>0.158</v>
       </c>
       <c r="G7">
-        <v>0.4109195402298851</v>
+        <v>0.2088091353996737</v>
       </c>
       <c r="H7">
-        <v>0.4109195402298851</v>
+        <v>0.2088091353996737</v>
       </c>
       <c r="I7">
-        <v>0.9310344827586208</v>
+        <v>0.2446982055464927</v>
       </c>
       <c r="J7">
-        <v>0.7844827586206897</v>
+        <v>0.2109336469517053</v>
       </c>
       <c r="K7">
-        <v>27.3</v>
+        <v>43.3</v>
       </c>
       <c r="L7">
-        <v>0.7844827586206897</v>
+        <v>0.7063621533442088</v>
       </c>
       <c r="M7">
-        <v>2.72</v>
+        <v>24.5</v>
       </c>
       <c r="N7">
-        <v>0.02158730158730159</v>
+        <v>0.05363397548161121</v>
       </c>
       <c r="O7">
-        <v>0.09963369963369964</v>
+        <v>0.5658198614318707</v>
       </c>
       <c r="P7">
-        <v>2.72</v>
+        <v>24.5</v>
       </c>
       <c r="Q7">
-        <v>0.02158730158730159</v>
+        <v>0.05363397548161121</v>
       </c>
       <c r="R7">
-        <v>0.09963369963369964</v>
+        <v>0.5658198614318707</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1267,70 +1285,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>6.17</v>
+        <v>51.7</v>
       </c>
       <c r="V7">
-        <v>0.04896825396825397</v>
+        <v>0.1131786339754816</v>
       </c>
       <c r="W7">
-        <v>0.3714285714285714</v>
+        <v>0.3205033308660252</v>
       </c>
       <c r="X7">
-        <v>0.04676810448916876</v>
+        <v>0.08240081756680576</v>
       </c>
       <c r="Y7">
-        <v>0.3246604669394027</v>
+        <v>0.2381025132992194</v>
       </c>
       <c r="Z7">
-        <v>0.5771144278606964</v>
+        <v>0.4201507882111035</v>
       </c>
       <c r="AA7">
-        <v>0.4527363184079602</v>
+        <v>0.08862393802700159</v>
       </c>
       <c r="AB7">
-        <v>0.04669657199083718</v>
+        <v>0.07561729194043204</v>
       </c>
       <c r="AC7">
-        <v>0.406039746417123</v>
+        <v>0.01300664608656955</v>
       </c>
       <c r="AD7">
-        <v>0.356</v>
+        <v>91.5</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0.356</v>
+        <v>91.5</v>
       </c>
       <c r="AG7">
-        <v>-5.814</v>
+        <v>39.8</v>
       </c>
       <c r="AH7">
-        <v>0.002817436449396942</v>
+        <v>0.1668794455590006</v>
       </c>
       <c r="AI7">
-        <v>0.003478056977607566</v>
+        <v>0.4052258635961027</v>
       </c>
       <c r="AJ7">
-        <v>-0.04837501872098247</v>
+        <v>0.0801449859041482</v>
       </c>
       <c r="AK7">
-        <v>-0.06044538706256627</v>
+        <v>0.2286042504307869</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AM7">
-        <v>-0.117</v>
+        <v>4.972</v>
       </c>
       <c r="AN7">
-        <v>0.01098765432098765</v>
+        <v>5.865384615384616</v>
+      </c>
+      <c r="AO7">
+        <v>2.918287937743191</v>
       </c>
       <c r="AP7">
-        <v>-0.1794444444444445</v>
+        <v>2.551282051282051</v>
       </c>
       <c r="AQ7">
-        <v>-276.9230769230769</v>
+        <v>3.016894609814964</v>
       </c>
     </row>
     <row r="8">
@@ -1341,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CapMan Oyj (HLSE:CAPMAN)</t>
+          <t>Taaleri Oyj (HLSE:TAALA)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1350,49 +1371,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.121</v>
+        <v>-0.006650000000000001</v>
       </c>
       <c r="E8">
-        <v>0.237</v>
-      </c>
-      <c r="F8">
-        <v>1.029</v>
+        <v>0.0653</v>
       </c>
       <c r="G8">
-        <v>0.1742043551088777</v>
+        <v>0.5230547550432276</v>
       </c>
       <c r="H8">
-        <v>0.1742043551088777</v>
+        <v>0.5230547550432276</v>
       </c>
       <c r="I8">
-        <v>0.2194304857621441</v>
+        <v>0.4034582132564841</v>
       </c>
       <c r="J8">
-        <v>0.1913314688070822</v>
+        <v>0.3121046118164273</v>
       </c>
       <c r="K8">
-        <v>37.2</v>
+        <v>25.1</v>
       </c>
       <c r="L8">
-        <v>0.6231155778894473</v>
+        <v>0.361671469740634</v>
       </c>
       <c r="M8">
-        <v>24.1</v>
+        <v>61.1</v>
       </c>
       <c r="N8">
-        <v>0.04478721427244007</v>
+        <v>0.180662329982259</v>
       </c>
       <c r="O8">
-        <v>0.6478494623655914</v>
+        <v>2.434262948207171</v>
       </c>
       <c r="P8">
-        <v>24.1</v>
+        <v>61.1</v>
       </c>
       <c r="Q8">
-        <v>0.04478721427244007</v>
+        <v>0.180662329982259</v>
       </c>
       <c r="R8">
-        <v>0.6478494623655914</v>
+        <v>2.434262948207171</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1401,73 +1419,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>0.126370563092362</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>0.3012145748987854</v>
+        <v>0.09812353401094605</v>
       </c>
       <c r="X8">
-        <v>0.05122979160740945</v>
+        <v>0.07767678771166531</v>
       </c>
       <c r="Y8">
-        <v>0.249984783291376</v>
+        <v>0.02044674629928074</v>
       </c>
       <c r="Z8">
-        <v>0.419831223628692</v>
+        <v>0.2549118276884199</v>
       </c>
       <c r="AA8">
-        <v>0.08032692466795222</v>
+        <v>0.07955915702811032</v>
       </c>
       <c r="AB8">
-        <v>0.04669053537451165</v>
+        <v>0.07619008609616612</v>
       </c>
       <c r="AC8">
-        <v>0.03363638929344057</v>
+        <v>0.003369070931944204</v>
       </c>
       <c r="AD8">
-        <v>96.5</v>
+        <v>14.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>96.5</v>
+        <v>14.6</v>
       </c>
       <c r="AG8">
-        <v>28.5</v>
+        <v>14.6</v>
       </c>
       <c r="AH8">
-        <v>0.1520642924676962</v>
+        <v>0.04138321995464853</v>
       </c>
       <c r="AI8">
-        <v>0.413985413985414</v>
+        <v>0.07087378640776699</v>
       </c>
       <c r="AJ8">
-        <v>0.05030003529827038</v>
+        <v>0.04138321995464853</v>
       </c>
       <c r="AK8">
-        <v>0.1726226529376136</v>
+        <v>0.07087378640776699</v>
       </c>
       <c r="AL8">
-        <v>4.93</v>
+        <v>0.951</v>
       </c>
       <c r="AM8">
-        <v>4.611</v>
+        <v>0.951</v>
       </c>
       <c r="AN8">
-        <v>7.043795620437956</v>
+        <v>0.5195729537366548</v>
       </c>
       <c r="AO8">
-        <v>2.657200811359027</v>
+        <v>29.44269190325973</v>
       </c>
       <c r="AP8">
-        <v>2.08029197080292</v>
+        <v>0.5195729537366548</v>
       </c>
       <c r="AQ8">
-        <v>2.841032314031664</v>
+        <v>29.44269190325973</v>
       </c>
     </row>
     <row r="9">
@@ -1478,7 +1496,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EAB Group Oyj (HLSE:EAB)</t>
+          <t>Sievi Capital Plc (HLSE:SIEVI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1487,46 +1505,46 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0536</v>
+        <v>-0.191</v>
       </c>
       <c r="E9">
-        <v>0.314</v>
+        <v>-0.24</v>
       </c>
       <c r="G9">
-        <v>0.1039669421487603</v>
+        <v>3.776683087027915</v>
       </c>
       <c r="H9">
-        <v>0.03537190082644628</v>
+        <v>3.776683087027915</v>
       </c>
       <c r="I9">
-        <v>0.09793388429752067</v>
+        <v>0.2939244663382595</v>
       </c>
       <c r="J9">
-        <v>0.08092997911179729</v>
+        <v>0.2939244663382595</v>
       </c>
       <c r="K9">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="L9">
-        <v>0.09297520661157026</v>
+        <v>0.5385878489326765</v>
       </c>
       <c r="M9">
-        <v>0.8142</v>
+        <v>0.024</v>
       </c>
       <c r="N9">
-        <v>0.01706918238993711</v>
+        <v>0.0003283173734610123</v>
       </c>
       <c r="O9">
-        <v>0.3618666666666667</v>
+        <v>0.007317073170731708</v>
       </c>
       <c r="P9">
-        <v>0.8142</v>
+        <v>0.024</v>
       </c>
       <c r="Q9">
-        <v>0.01706918238993711</v>
+        <v>0.0003283173734610123</v>
       </c>
       <c r="R9">
-        <v>0.3618666666666667</v>
+        <v>0.007317073170731708</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1535,73 +1553,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>2.02</v>
+        <v>3.35</v>
       </c>
       <c r="V9">
-        <v>0.04234800838574423</v>
+        <v>0.04582763337893297</v>
       </c>
       <c r="W9">
-        <v>0.108695652173913</v>
+        <v>0.03215686274509804</v>
       </c>
       <c r="X9">
-        <v>0.05166206871275896</v>
+        <v>0.08077946090680761</v>
       </c>
       <c r="Y9">
-        <v>0.05703358346115408</v>
+        <v>-0.04862259816170957</v>
       </c>
       <c r="Z9">
-        <v>0.8926595352268536</v>
+        <v>0.06331482752167676</v>
       </c>
       <c r="AA9">
-        <v>0.07224291753985594</v>
+        <v>0.01860977689060778</v>
       </c>
       <c r="AB9">
-        <v>0.04669004515281631</v>
+        <v>0.07658272410932017</v>
       </c>
       <c r="AC9">
-        <v>0.02555287238703963</v>
+        <v>-0.05797294721871239</v>
       </c>
       <c r="AD9">
-        <v>9.369999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>9.369999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="AG9">
         <v>7.35</v>
       </c>
       <c r="AH9">
-        <v>0.1641843350271596</v>
+        <v>0.1276849642004773</v>
       </c>
       <c r="AI9">
-        <v>0.2841977555353352</v>
+        <v>0.1030828516377649</v>
       </c>
       <c r="AJ9">
-        <v>0.1335149863760218</v>
+        <v>0.09136109384711001</v>
       </c>
       <c r="AK9">
-        <v>0.2374798061389337</v>
+        <v>0.07317073170731708</v>
       </c>
       <c r="AL9">
-        <v>0.474</v>
+        <v>0.12</v>
       </c>
       <c r="AM9">
-        <v>0.355</v>
+        <v>0.12</v>
       </c>
       <c r="AN9">
-        <v>3.432234432234432</v>
+        <v>5.911602209944751</v>
       </c>
       <c r="AO9">
-        <v>5.000000000000001</v>
+        <v>14.91666666666667</v>
       </c>
       <c r="AP9">
-        <v>2.692307692307692</v>
+        <v>4.060773480662983</v>
       </c>
       <c r="AQ9">
-        <v>6.67605633802817</v>
+        <v>14.91666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -1620,119 +1638,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="F10">
-        <v>0.275</v>
-      </c>
       <c r="G10">
-        <v>0.08235294117647059</v>
+        <v>0.1155015197568389</v>
       </c>
       <c r="H10">
-        <v>0.08235294117647059</v>
+        <v>0.1155015197568389</v>
       </c>
       <c r="I10">
-        <v>0.02142857142857143</v>
+        <v>-0.04214792299898683</v>
       </c>
       <c r="J10">
-        <v>0.01829268292682927</v>
+        <v>-0.04214792299898683</v>
       </c>
       <c r="K10">
-        <v>7.3</v>
+        <v>-6.31</v>
       </c>
       <c r="L10">
-        <v>0.1022408963585434</v>
+        <v>-0.06393110435663626</v>
       </c>
       <c r="M10">
-        <v>4.73</v>
+        <v>3.02</v>
       </c>
       <c r="N10">
-        <v>0.05180722891566265</v>
+        <v>0.1037800687285223</v>
       </c>
       <c r="O10">
-        <v>0.6479452054794521</v>
+        <v>-0.4786053882725833</v>
       </c>
       <c r="P10">
-        <v>4.69</v>
+        <v>3.02</v>
       </c>
       <c r="Q10">
-        <v>0.05136911281489595</v>
+        <v>0.1037800687285223</v>
       </c>
       <c r="R10">
-        <v>0.6424657534246576</v>
+        <v>-0.4786053882725833</v>
       </c>
       <c r="S10">
-        <v>0.04000000000000004</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>0.008456659619450324</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>14</v>
+        <v>9.17</v>
       </c>
       <c r="V10">
-        <v>0.1533406352683461</v>
+        <v>0.3151202749140893</v>
       </c>
       <c r="W10">
-        <v>0.09554973821989528</v>
+        <v>-0.07602409638554217</v>
       </c>
       <c r="X10">
-        <v>0.05771572735668416</v>
+        <v>0.1202856677436954</v>
       </c>
       <c r="Y10">
-        <v>0.03783401086321111</v>
+        <v>-0.1963097641292376</v>
       </c>
       <c r="Z10">
-        <v>0.9492156341398565</v>
+        <v>1.17921146953405</v>
       </c>
       <c r="AA10">
-        <v>0.01736370062450957</v>
+        <v>-0.04970131421744325</v>
       </c>
       <c r="AB10">
-        <v>0.04668440678527066</v>
+        <v>0.07366975161655316</v>
       </c>
       <c r="AC10">
-        <v>-0.02932070616076109</v>
+        <v>-0.1233710658339964</v>
       </c>
       <c r="AD10">
-        <v>39.8</v>
+        <v>42.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>39.8</v>
+        <v>42.5</v>
       </c>
       <c r="AG10">
-        <v>25.8</v>
+        <v>33.33</v>
       </c>
       <c r="AH10">
-        <v>0.3035850495804729</v>
+        <v>0.5935754189944135</v>
       </c>
       <c r="AI10">
-        <v>0.314873417721519</v>
+        <v>0.391705069124424</v>
       </c>
       <c r="AJ10">
-        <v>0.2203245089666951</v>
+        <v>0.5338779432964921</v>
       </c>
       <c r="AK10">
-        <v>0.2295373665480427</v>
+        <v>0.3355481727574751</v>
       </c>
       <c r="AL10">
-        <v>2.23</v>
+        <v>4.67</v>
       </c>
       <c r="AM10">
-        <v>0.4199999999999999</v>
+        <v>3.48</v>
       </c>
       <c r="AN10">
-        <v>6.337579617834394</v>
+        <v>12.61127596439169</v>
       </c>
       <c r="AO10">
-        <v>0.6860986547085202</v>
+        <v>-0.8907922912205568</v>
       </c>
       <c r="AP10">
-        <v>4.108280254777069</v>
+        <v>9.890207715133529</v>
       </c>
       <c r="AQ10">
-        <v>3.642857142857144</v>
+        <v>-1.195402298850575</v>
       </c>
     </row>
     <row r="11">
@@ -1743,7 +1758,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Evli Bank plc (HLSE:EVLI)</t>
+          <t>Eagle Filters Group Oyj (HLSE:EAGLE)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1752,109 +1767,115 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.118</v>
-      </c>
-      <c r="E11">
-        <v>0.226</v>
+        <v>-0.147</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>-4.365168539325843</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>-4.365168539325843</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>-4.471910112359551</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>-4.471910112359551</v>
       </c>
       <c r="K11">
-        <v>41.6</v>
+        <v>-0.547</v>
       </c>
       <c r="L11">
-        <v>0.3304209690230341</v>
+        <v>-3.073033707865169</v>
       </c>
       <c r="M11">
-        <v>20.2194</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.02857058075455701</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.4860432692307691</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>20.2194</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.02857058075455701</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.4860432692307691</v>
+        <v>0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>0</v>
+        <v>0.278</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>0.03228803716608595</v>
       </c>
       <c r="W11">
-        <v>0.4378947368421053</v>
+        <v>-0.04972727272727273</v>
       </c>
       <c r="X11">
-        <v>0.05149713200327474</v>
+        <v>0.08786652349135464</v>
       </c>
       <c r="Y11">
-        <v>0.3863976048388306</v>
+        <v>-0.1375937962186274</v>
       </c>
       <c r="Z11">
-        <v>0.383373934226553</v>
+        <v>0.01164007324091028</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>-0.05205336123463249</v>
       </c>
       <c r="AB11">
-        <v>0.04669023053595162</v>
+        <v>0.07682015113052301</v>
       </c>
       <c r="AC11">
-        <v>-0.04669023053595162</v>
+        <v>-0.1288735123651555</v>
       </c>
       <c r="AD11">
-        <v>134.4</v>
+        <v>3.29</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>134.4</v>
+        <v>3.29</v>
       </c>
       <c r="AG11">
-        <v>134.4</v>
+        <v>3.012</v>
       </c>
       <c r="AH11">
-        <v>0.1596009975062344</v>
+        <v>0.2764705882352941</v>
       </c>
       <c r="AI11">
-        <v>0.48068669527897</v>
+        <v>0.2044748290863891</v>
       </c>
       <c r="AJ11">
-        <v>0.1596009975062344</v>
+        <v>0.2591636551368095</v>
       </c>
       <c r="AK11">
-        <v>0.48068669527897</v>
+        <v>0.1904882367821907</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.414</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.299</v>
+      </c>
+      <c r="AN11">
+        <v>-4.148802017654477</v>
+      </c>
+      <c r="AO11">
+        <v>-1.922705314009662</v>
+      </c>
+      <c r="AP11">
+        <v>-3.798234552332913</v>
+      </c>
+      <c r="AQ11">
+        <v>-2.662207357859532</v>
       </c>
     </row>
     <row r="12">
@@ -1865,7 +1886,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Loudspring Oyj (HLSE:LOUD)</t>
+          <t>Lifeline SPAC I Oyj (HLSE:LL1SPAC)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1873,26 +1894,8 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.0481</v>
-      </c>
-      <c r="G12">
-        <v>-4.52112676056338</v>
-      </c>
-      <c r="H12">
-        <v>-4.52112676056338</v>
-      </c>
-      <c r="I12">
-        <v>-4.502347417840376</v>
-      </c>
-      <c r="J12">
-        <v>-4.502347417840376</v>
-      </c>
       <c r="K12">
-        <v>-2.13</v>
-      </c>
-      <c r="L12">
-        <v>-10</v>
+        <v>-19.6</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1916,156 +1919,52 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>0.918</v>
+        <v>1.97</v>
       </c>
       <c r="V12">
-        <v>0.09300911854103344</v>
-      </c>
-      <c r="W12">
-        <v>-0.2502937720329025</v>
+        <v>0.014668652271035</v>
       </c>
       <c r="X12">
-        <v>0.0600396430943544</v>
-      </c>
-      <c r="Y12">
-        <v>-0.3103334151272569</v>
-      </c>
-      <c r="Z12">
-        <v>0.01682331569386305</v>
-      </c>
-      <c r="AA12">
-        <v>-0.07574441197377774</v>
+        <v>0.09948038104377877</v>
       </c>
       <c r="AB12">
-        <v>0.04795904382939527</v>
-      </c>
-      <c r="AC12">
-        <v>-0.123703455803173</v>
+        <v>0.0783933310665597</v>
       </c>
       <c r="AD12">
-        <v>5.21</v>
+        <v>103.2</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>5.21</v>
+        <v>103.2</v>
       </c>
       <c r="AG12">
-        <v>4.292</v>
+        <v>101.23</v>
       </c>
       <c r="AH12">
-        <v>0.3454907161803714</v>
+        <v>0.4345263157894737</v>
       </c>
       <c r="AI12">
-        <v>0.3214065391733498</v>
+        <v>0.971934450932379</v>
       </c>
       <c r="AJ12">
-        <v>0.3030645389069341</v>
+        <v>0.4297966288795482</v>
       </c>
       <c r="AK12">
-        <v>0.2806696311797018</v>
+        <v>0.9714038959792726</v>
       </c>
       <c r="AL12">
-        <v>0.458</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AM12">
-        <v>-0.03799999999999998</v>
-      </c>
-      <c r="AN12">
-        <v>-5.444096133751306</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AO12">
-        <v>-2.093886462882096</v>
-      </c>
-      <c r="AP12">
-        <v>-4.484848484848484</v>
+        <v>-33.98576512455516</v>
       </c>
       <c r="AQ12">
-        <v>25.23684210526317</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Finland</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Virala Acquisition Company Oyj (HLSE:VACSPAC)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Investments &amp; Asset Management</t>
-        </is>
-      </c>
-      <c r="K13">
-        <v>-2.92</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>4.64</v>
-      </c>
-      <c r="V13">
-        <v>0.00698584763625414</v>
-      </c>
-      <c r="X13">
-        <v>0.0466966859482318</v>
-      </c>
-      <c r="AB13">
-        <v>0.0466966859482318</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>-4.64</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>-0.007034993025653465</v>
-      </c>
-      <c r="AK13">
-        <v>-0.04144337263308324</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
+        <v>-33.98576512455516</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_investments_asset_management.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.073175</v>
+        <v>0.141</v>
       </c>
       <c r="E2">
-        <v>0.104</v>
+        <v>0.08995</v>
       </c>
       <c r="F2">
-        <v>0.158</v>
+        <v>0.077</v>
       </c>
       <c r="G2">
-        <v>0.4730197880370492</v>
+        <v>0.2177242257003399</v>
       </c>
       <c r="H2">
-        <v>0.4730197880370492</v>
+        <v>0.2177242257003399</v>
       </c>
       <c r="I2">
-        <v>0.285758290032094</v>
+        <v>0.1963306267457426</v>
       </c>
       <c r="J2">
-        <v>0.251815903618762</v>
+        <v>0.1754815648561784</v>
       </c>
       <c r="K2">
-        <v>133.773</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="L2">
-        <v>0.2691241439803005</v>
+        <v>0.1188216248067478</v>
       </c>
       <c r="M2">
-        <v>186.735</v>
+        <v>138.039</v>
       </c>
       <c r="N2">
-        <v>0.06657432858808304</v>
+        <v>0.05622082841200667</v>
       </c>
       <c r="O2">
-        <v>1.395909488461797</v>
+        <v>1.764302147239264</v>
       </c>
       <c r="P2">
-        <v>185.344</v>
+        <v>137.72</v>
       </c>
       <c r="Q2">
-        <v>0.06607841249808372</v>
+        <v>0.05609090538834358</v>
       </c>
       <c r="R2">
-        <v>1.385511276565525</v>
+        <v>1.760224948875256</v>
       </c>
       <c r="S2">
-        <v>1.390999999999999</v>
+        <v>0.3190000000000008</v>
       </c>
       <c r="T2">
-        <v>0.007449058826679514</v>
+        <v>0.002310941110845492</v>
       </c>
       <c r="U2">
-        <v>79.89500000000001</v>
+        <v>91.029</v>
       </c>
       <c r="V2">
-        <v>0.02848397987814226</v>
+        <v>0.03707449191544821</v>
       </c>
       <c r="W2">
-        <v>0.1699499249002099</v>
+        <v>0.1138898248508934</v>
       </c>
       <c r="X2">
-        <v>0.08159013923680669</v>
+        <v>0.07025929807576026</v>
       </c>
       <c r="Y2">
-        <v>0.08835978566340316</v>
+        <v>0.04363052677513313</v>
       </c>
       <c r="Z2">
-        <v>0.6795294878988057</v>
+        <v>0.5592211425792086</v>
       </c>
       <c r="AA2">
-        <v>0.08409154752755596</v>
+        <v>0.1294085696805209</v>
       </c>
       <c r="AB2">
-        <v>0.07636713008016621</v>
+        <v>0.06499472126733657</v>
       </c>
       <c r="AC2">
-        <v>0.008187858509256879</v>
+        <v>0.0646905951813041</v>
       </c>
       <c r="AD2">
-        <v>386.55</v>
+        <v>580.27</v>
       </c>
       <c r="AE2">
-        <v>0.008491451635729707</v>
+        <v>0.04478764618916383</v>
       </c>
       <c r="AF2">
-        <v>386.5584914516357</v>
+        <v>580.3147876461892</v>
       </c>
       <c r="AG2">
-        <v>306.6634914516358</v>
+        <v>489.2857876461892</v>
       </c>
       <c r="AH2">
-        <v>0.1211224527163701</v>
+        <v>0.1911687839998185</v>
       </c>
       <c r="AI2">
-        <v>0.3473314063811712</v>
+        <v>0.4335480321337039</v>
       </c>
       <c r="AJ2">
-        <v>0.09855576038751016</v>
+        <v>0.1661645551978667</v>
       </c>
       <c r="AK2">
-        <v>0.2968543860827305</v>
+        <v>0.3922143805947334</v>
       </c>
       <c r="AL2">
-        <v>13.372</v>
+        <v>28.544</v>
       </c>
       <c r="AM2">
-        <v>11.834</v>
+        <v>22.733</v>
       </c>
       <c r="AN2">
-        <v>2.237030949790505</v>
+        <v>3.698437181317561</v>
       </c>
       <c r="AO2">
-        <v>10.62174693389171</v>
+        <v>4.527711603139013</v>
       </c>
       <c r="AP2">
-        <v>1.774714064281788</v>
+        <v>3.118535766661924</v>
       </c>
       <c r="AQ2">
-        <v>12.0021970593206</v>
+        <v>5.685083358993534</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Evli Oyj (HLSE:EVLI)</t>
+          <t>Titanium Oyj (HLSE:TITAN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,101 +724,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.163</v>
+      </c>
+      <c r="E3">
+        <v>0.211</v>
+      </c>
       <c r="G3">
-        <v>0.6321393998063891</v>
+        <v>0.6622516556291391</v>
       </c>
       <c r="H3">
-        <v>0.6321393998063891</v>
+        <v>0.6622516556291391</v>
       </c>
       <c r="I3">
-        <v>0.4114230396902226</v>
+        <v>0.5794701986754967</v>
       </c>
       <c r="J3">
-        <v>0.3268854008205412</v>
+        <v>0.444883571886349</v>
       </c>
       <c r="K3">
-        <v>28.9</v>
+        <v>11.9</v>
       </c>
       <c r="L3">
-        <v>0.2797676669893514</v>
+        <v>0.3940397350993378</v>
       </c>
       <c r="M3">
-        <v>42.684</v>
+        <v>10.3</v>
       </c>
       <c r="N3">
-        <v>0.1003385049365303</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="O3">
-        <v>1.476955017301038</v>
+        <v>0.865546218487395</v>
       </c>
       <c r="P3">
-        <v>41.9</v>
+        <v>10.3</v>
       </c>
       <c r="Q3">
-        <v>0.09849553361542078</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="R3">
-        <v>1.449826989619377</v>
+        <v>0.865546218487395</v>
       </c>
       <c r="S3">
-        <v>0.7839999999999989</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01836753818761126</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.06131834440470108</v>
+      </c>
+      <c r="W3">
+        <v>0.5509259259259259</v>
       </c>
       <c r="X3">
-        <v>0.08396189941187253</v>
+        <v>0.06529514774554175</v>
+      </c>
+      <c r="Y3">
+        <v>0.4856307781803842</v>
+      </c>
+      <c r="Z3">
+        <v>4.148351648351647</v>
+      </c>
+      <c r="AA3">
+        <v>1.845533498759305</v>
       </c>
       <c r="AB3">
-        <v>0.0773127357958221</v>
+        <v>0.06529514774554175</v>
+      </c>
+      <c r="AC3">
+        <v>1.780238351013763</v>
       </c>
       <c r="AD3">
-        <v>107.3</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>107.3</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>107.3</v>
+        <v>-12</v>
       </c>
       <c r="AH3">
-        <v>0.2014266941993618</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.5208737864077669</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.2014266941993618</v>
+        <v>-0.065323897659227</v>
       </c>
       <c r="AK3">
-        <v>0.5208737864077669</v>
+        <v>-1.621621621621622</v>
       </c>
       <c r="AL3">
-        <v>0.981</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AM3">
-        <v>0.981</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AN3">
-        <v>2.495348837209302</v>
+        <v>0</v>
       </c>
       <c r="AO3">
-        <v>43.32313965341488</v>
+        <v>198.8636363636364</v>
       </c>
       <c r="AP3">
-        <v>2.495348837209302</v>
+        <v>-0.6153846153846154</v>
       </c>
       <c r="AQ3">
-        <v>43.32313965341488</v>
+        <v>198.8636363636364</v>
       </c>
     </row>
     <row r="4">
@@ -829,7 +850,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Titanium Oyj (HLSE:TITAN)</t>
+          <t>eQ Oyj (HLSE:EQV1V)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -838,46 +859,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.244</v>
+        <v>0.0818</v>
       </c>
       <c r="E4">
-        <v>0.303</v>
+        <v>0.101</v>
       </c>
       <c r="G4">
-        <v>0.644927536231884</v>
+        <v>0.699290780141844</v>
       </c>
       <c r="H4">
-        <v>0.644927536231884</v>
+        <v>0.699290780141844</v>
       </c>
       <c r="I4">
-        <v>0.6086956521739131</v>
+        <v>0.5466389002944988</v>
       </c>
       <c r="J4">
-        <v>0.4703188405797101</v>
+        <v>0.4330405038270483</v>
       </c>
       <c r="K4">
-        <v>11.6</v>
+        <v>30.4</v>
       </c>
       <c r="L4">
-        <v>0.4202898550724637</v>
+        <v>0.4312056737588652</v>
       </c>
       <c r="M4">
-        <v>9.720000000000001</v>
+        <v>38.9</v>
       </c>
       <c r="N4">
-        <v>0.05700879765395895</v>
+        <v>0.05543679635171725</v>
       </c>
       <c r="O4">
-        <v>0.8379310344827587</v>
+        <v>1.279605263157895</v>
       </c>
       <c r="P4">
-        <v>9.720000000000001</v>
+        <v>38.9</v>
       </c>
       <c r="Q4">
-        <v>0.05700879765395895</v>
+        <v>0.05543679635171725</v>
       </c>
       <c r="R4">
-        <v>0.8379310344827587</v>
+        <v>1.279605263157895</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,73 +907,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>13.4</v>
+        <v>0.03</v>
       </c>
       <c r="V4">
-        <v>0.07859237536656892</v>
+        <v>4.275331338178708e-05</v>
       </c>
       <c r="W4">
-        <v>0.5272727272727272</v>
+        <v>0.4047936085219707</v>
       </c>
       <c r="X4">
-        <v>0.07659232036578076</v>
+        <v>0.06546233602135874</v>
       </c>
       <c r="Y4">
-        <v>0.4506804069069464</v>
+        <v>0.339331272500612</v>
       </c>
       <c r="Z4">
-        <v>4.276417725441586</v>
+        <v>0.8705016157249894</v>
       </c>
       <c r="AA4">
-        <v>2.011279826464208</v>
+        <v>0.3769624582558089</v>
       </c>
       <c r="AB4">
-        <v>0.07634680571615854</v>
+        <v>0.06525929067175955</v>
       </c>
       <c r="AC4">
-        <v>1.934933020748049</v>
+        <v>0.3117031675840494</v>
       </c>
       <c r="AD4">
-        <v>1.21</v>
+        <v>5.49</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.04478764618916383</v>
       </c>
       <c r="AF4">
-        <v>1.21</v>
+        <v>5.534787646189164</v>
       </c>
       <c r="AG4">
-        <v>-12.19</v>
+        <v>5.504787646189164</v>
       </c>
       <c r="AH4">
-        <v>0.007046764894298526</v>
+        <v>0.007825955033419639</v>
       </c>
       <c r="AI4">
-        <v>0.0530469092503288</v>
+        <v>0.07212879341908279</v>
       </c>
       <c r="AJ4">
-        <v>-0.07700082117364665</v>
+        <v>0.007783866487260236</v>
       </c>
       <c r="AK4">
-        <v>-1.295430393198725</v>
+        <v>0.07176589382635039</v>
       </c>
       <c r="AL4">
-        <v>0.227</v>
+        <v>0.163</v>
       </c>
       <c r="AM4">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AN4">
-        <v>0.06368421052631579</v>
+        <v>0.1405997899966707</v>
       </c>
       <c r="AO4">
-        <v>74.00881057268722</v>
+        <v>236.1963190184049</v>
       </c>
       <c r="AP4">
-        <v>-0.6415789473684211</v>
+        <v>0.1409785040128349</v>
       </c>
       <c r="AQ4">
-        <v>103.7037037037037</v>
+        <v>236.1963190184049</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +984,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>eQ Oyj (HLSE:EQV1V)</t>
+          <t>Alexandria Group Oyj (HLSE:ALEX)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -971,122 +992,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D5">
-        <v>0.188</v>
-      </c>
-      <c r="E5">
-        <v>0.253</v>
-      </c>
       <c r="G5">
-        <v>0.6484560570071259</v>
+        <v>0.1780487804878049</v>
       </c>
       <c r="H5">
-        <v>0.6484560570071259</v>
+        <v>0.1780487804878049</v>
       </c>
       <c r="I5">
-        <v>0.606975079687326</v>
+        <v>0.1760975609756097</v>
       </c>
       <c r="J5">
-        <v>0.4834419910621168</v>
+        <v>0.1362693565546318</v>
       </c>
       <c r="K5">
-        <v>40.7</v>
+        <v>4.31</v>
       </c>
       <c r="L5">
-        <v>0.4833729216152019</v>
+        <v>0.1051219512195122</v>
       </c>
       <c r="M5">
-        <v>37.7</v>
+        <v>5.027</v>
       </c>
       <c r="N5">
-        <v>0.03428519461622408</v>
+        <v>0.07080281690140845</v>
       </c>
       <c r="O5">
-        <v>0.9262899262899263</v>
+        <v>1.166357308584687</v>
       </c>
       <c r="P5">
-        <v>37.7</v>
+        <v>4.72</v>
       </c>
       <c r="Q5">
-        <v>0.03428519461622408</v>
+        <v>0.06647887323943662</v>
       </c>
       <c r="R5">
-        <v>0.9262899262899263</v>
+        <v>1.095127610208817</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.3070000000000004</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.06107022080763883</v>
       </c>
       <c r="U5">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>2.455438341214987e-05</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>0.5030902348578492</v>
+        <v>0.1431893687707641</v>
       </c>
       <c r="X5">
-        <v>0.07653968735088998</v>
+        <v>0.06708636900157838</v>
       </c>
       <c r="Y5">
-        <v>0.4265505475069592</v>
+        <v>0.07610299976918572</v>
       </c>
       <c r="Z5">
-        <v>1.020785577174739</v>
+        <v>1.431564245810056</v>
       </c>
       <c r="AA5">
-        <v>0.493490611876848</v>
+        <v>0.195078338643153</v>
       </c>
       <c r="AB5">
-        <v>0.07638745444417389</v>
+        <v>0.06493812324369071</v>
       </c>
       <c r="AC5">
-        <v>0.4171031574326741</v>
+        <v>0.1301402153994623</v>
       </c>
       <c r="AD5">
-        <v>5.87</v>
+        <v>6</v>
       </c>
       <c r="AE5">
-        <v>0.008491451635729707</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>5.87849145163573</v>
+        <v>6</v>
       </c>
       <c r="AG5">
-        <v>5.85149145163573</v>
+        <v>6</v>
       </c>
       <c r="AH5">
-        <v>0.005317599118474493</v>
+        <v>0.07792207792207792</v>
       </c>
       <c r="AI5">
-        <v>0.07259324477718444</v>
+        <v>0.1591511936339522</v>
       </c>
       <c r="AJ5">
-        <v>0.005293304588111579</v>
+        <v>0.07792207792207792</v>
       </c>
       <c r="AK5">
-        <v>0.07228392394884645</v>
+        <v>0.1591511936339522</v>
       </c>
       <c r="AL5">
-        <v>0.043</v>
+        <v>0.203</v>
       </c>
       <c r="AM5">
-        <v>0.043</v>
+        <v>0.203</v>
       </c>
       <c r="AN5">
-        <v>0.1139606670678911</v>
+        <v>0.7822685788787483</v>
       </c>
       <c r="AO5">
-        <v>1188.372093023256</v>
+        <v>35.56650246305419</v>
       </c>
       <c r="AP5">
-        <v>0.1136013405741857</v>
+        <v>0.7822685788787483</v>
       </c>
       <c r="AQ5">
-        <v>1188.372093023256</v>
+        <v>35.56650246305419</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alexandria Pankkiiriliike Oyj (HLSE:ALEX)</t>
+          <t>Evli Oyj (HLSE:EVLI)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1106,46 +1121,46 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.3174946004319654</v>
+        <v>0.2905911740216486</v>
       </c>
       <c r="H6">
-        <v>0.3174946004319654</v>
+        <v>0.2905911740216486</v>
       </c>
       <c r="I6">
-        <v>0.2354211663066955</v>
+        <v>0.3305578684429643</v>
       </c>
       <c r="J6">
-        <v>0.1913838399500336</v>
+        <v>0.2679066801540498</v>
       </c>
       <c r="K6">
-        <v>7.35</v>
+        <v>26.4</v>
       </c>
       <c r="L6">
-        <v>0.1587473002159827</v>
+        <v>0.2198168193172356</v>
       </c>
       <c r="M6">
-        <v>7.987</v>
+        <v>32</v>
       </c>
       <c r="N6">
-        <v>0.1152525252525253</v>
+        <v>0.05548812207386856</v>
       </c>
       <c r="O6">
-        <v>1.086666666666667</v>
+        <v>1.212121212121212</v>
       </c>
       <c r="P6">
-        <v>7.38</v>
+        <v>32</v>
       </c>
       <c r="Q6">
-        <v>0.1064935064935065</v>
+        <v>0.05548812207386856</v>
       </c>
       <c r="R6">
-        <v>1.004081632653061</v>
+        <v>1.212121212121212</v>
       </c>
       <c r="S6">
-        <v>0.6070000000000002</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.07599849755853263</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -1154,67 +1169,67 @@
         <v>0</v>
       </c>
       <c r="W6">
-        <v>0.2417763157894737</v>
+        <v>0.2787750791974656</v>
       </c>
       <c r="X6">
-        <v>0.07914668967774546</v>
+        <v>0.06996660018661456</v>
       </c>
       <c r="Y6">
-        <v>0.1626296261117282</v>
+        <v>0.2088084790108511</v>
       </c>
       <c r="Z6">
-        <v>1.584531143052704</v>
+        <v>0.5945544554455445</v>
       </c>
       <c r="AA6">
-        <v>0.3032536546778424</v>
+        <v>0.1592851103292147</v>
       </c>
       <c r="AB6">
-        <v>0.07599419324955703</v>
+        <v>0.06446771294108368</v>
       </c>
       <c r="AC6">
-        <v>0.2272594614282853</v>
+        <v>0.09481739738813107</v>
       </c>
       <c r="AD6">
-        <v>6.38</v>
+        <v>127.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>6.38</v>
+        <v>127.1</v>
       </c>
       <c r="AG6">
-        <v>6.38</v>
+        <v>127.1</v>
       </c>
       <c r="AH6">
-        <v>0.08430232558139536</v>
+        <v>0.1805910770105143</v>
       </c>
       <c r="AI6">
-        <v>0.1734638390429581</v>
+        <v>0.4781790820165538</v>
       </c>
       <c r="AJ6">
-        <v>0.08430232558139536</v>
+        <v>0.1805910770105143</v>
       </c>
       <c r="AK6">
-        <v>0.1734638390429581</v>
+        <v>0.4781790820165538</v>
       </c>
       <c r="AL6">
-        <v>0.264</v>
+        <v>3.7</v>
       </c>
       <c r="AM6">
-        <v>0.264</v>
+        <v>3.7</v>
       </c>
       <c r="AN6">
-        <v>0.5696428571428571</v>
+        <v>3.1775</v>
       </c>
       <c r="AO6">
-        <v>41.28787878787879</v>
+        <v>10.72972972972973</v>
       </c>
       <c r="AP6">
-        <v>0.5696428571428571</v>
+        <v>3.1775</v>
       </c>
       <c r="AQ6">
-        <v>41.28787878787879</v>
+        <v>10.72972972972973</v>
       </c>
     </row>
     <row r="7">
@@ -1225,7 +1240,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CapMan Oyj (HLSE:CAPMAN)</t>
+          <t>Taaleri Oyj (HLSE:TAALA)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1234,49 +1249,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.153</v>
+        <v>-0.0108</v>
       </c>
       <c r="E7">
-        <v>0.104</v>
-      </c>
-      <c r="F7">
-        <v>0.158</v>
+        <v>0.043</v>
       </c>
       <c r="G7">
-        <v>0.2088091353996737</v>
+        <v>0.3732782369146006</v>
       </c>
       <c r="H7">
-        <v>0.2088091353996737</v>
+        <v>0.3732782369146006</v>
       </c>
       <c r="I7">
-        <v>0.2446982055464927</v>
+        <v>0.4917355371900827</v>
       </c>
       <c r="J7">
-        <v>0.2109336469517053</v>
+        <v>0.431651134165641</v>
       </c>
       <c r="K7">
-        <v>43.3</v>
+        <v>26</v>
       </c>
       <c r="L7">
-        <v>0.7063621533442088</v>
+        <v>0.3581267217630854</v>
       </c>
       <c r="M7">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="N7">
-        <v>0.05363397548161121</v>
+        <v>0.07470651013874066</v>
       </c>
       <c r="O7">
-        <v>0.5658198614318707</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="P7">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="Q7">
-        <v>0.05363397548161121</v>
+        <v>0.07470651013874066</v>
       </c>
       <c r="R7">
-        <v>0.5658198614318707</v>
+        <v>0.8076923076923077</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1285,73 +1297,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>51.7</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>0.1131786339754816</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.3205033308660252</v>
+        <v>0.1359121798222687</v>
       </c>
       <c r="X7">
-        <v>0.08240081756680576</v>
+        <v>0.06648653396931851</v>
       </c>
       <c r="Y7">
-        <v>0.2381025132992194</v>
+        <v>0.06942564585295018</v>
       </c>
       <c r="Z7">
-        <v>0.4201507882111035</v>
+        <v>0.3531815528312901</v>
       </c>
       <c r="AA7">
-        <v>0.08862393802700159</v>
+        <v>0.1524512178460086</v>
       </c>
       <c r="AB7">
-        <v>0.07561729194043204</v>
+        <v>0.06505131929098243</v>
       </c>
       <c r="AC7">
-        <v>0.01300664608656955</v>
+        <v>0.0873998985550262</v>
       </c>
       <c r="AD7">
-        <v>91.5</v>
+        <v>15.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>91.5</v>
+        <v>15.8</v>
       </c>
       <c r="AG7">
-        <v>39.8</v>
+        <v>15.8</v>
       </c>
       <c r="AH7">
-        <v>0.1668794455590006</v>
+        <v>0.05321657123610643</v>
       </c>
       <c r="AI7">
-        <v>0.4052258635961027</v>
+        <v>0.06757912745936698</v>
       </c>
       <c r="AJ7">
-        <v>0.0801449859041482</v>
+        <v>0.05321657123610643</v>
       </c>
       <c r="AK7">
-        <v>0.2286042504307869</v>
+        <v>0.06757912745936698</v>
       </c>
       <c r="AL7">
-        <v>5.14</v>
+        <v>1.3</v>
       </c>
       <c r="AM7">
-        <v>4.972</v>
+        <v>1.3</v>
       </c>
       <c r="AN7">
-        <v>5.865384615384616</v>
+        <v>0.4450704225352113</v>
       </c>
       <c r="AO7">
-        <v>2.918287937743191</v>
+        <v>27.46153846153846</v>
       </c>
       <c r="AP7">
-        <v>2.551282051282051</v>
+        <v>0.4450704225352113</v>
       </c>
       <c r="AQ7">
-        <v>3.016894609814964</v>
+        <v>27.46153846153846</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1374,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Taaleri Oyj (HLSE:TAALA)</t>
+          <t>CapMan Oyj (HLSE:CAPMAN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,121 +1383,124 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.006650000000000001</v>
+        <v>0.141</v>
       </c>
       <c r="E8">
-        <v>0.0653</v>
+        <v>0.0789</v>
+      </c>
+      <c r="F8">
+        <v>0.077</v>
       </c>
       <c r="G8">
-        <v>0.5230547550432276</v>
+        <v>0.3052325581395349</v>
       </c>
       <c r="H8">
-        <v>0.5230547550432276</v>
+        <v>0.3052325581395349</v>
       </c>
       <c r="I8">
-        <v>0.4034582132564841</v>
+        <v>0.2659883720930233</v>
       </c>
       <c r="J8">
-        <v>0.3121046118164273</v>
+        <v>0.2436521690518784</v>
       </c>
       <c r="K8">
-        <v>25.1</v>
+        <v>12.2</v>
       </c>
       <c r="L8">
-        <v>0.361671469740634</v>
+        <v>0.1773255813953488</v>
       </c>
       <c r="M8">
-        <v>61.1</v>
+        <v>30.812</v>
       </c>
       <c r="N8">
-        <v>0.180662329982259</v>
+        <v>0.07664676616915424</v>
       </c>
       <c r="O8">
-        <v>2.434262948207171</v>
+        <v>2.525573770491803</v>
       </c>
       <c r="P8">
-        <v>61.1</v>
+        <v>30.8</v>
       </c>
       <c r="Q8">
-        <v>0.180662329982259</v>
+        <v>0.07661691542288557</v>
       </c>
       <c r="R8">
-        <v>2.434262948207171</v>
+        <v>2.524590163934426</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>0.01200000000000045</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.0003894586524730772</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>0.1236318407960199</v>
       </c>
       <c r="W8">
-        <v>0.09812353401094605</v>
+        <v>0.09186746987951806</v>
       </c>
       <c r="X8">
-        <v>0.07767678771166531</v>
+        <v>0.07055199596490595</v>
       </c>
       <c r="Y8">
-        <v>0.02044674629928074</v>
+        <v>0.02131547391461211</v>
       </c>
       <c r="Z8">
-        <v>0.2549118276884199</v>
+        <v>0.4365482233502537</v>
       </c>
       <c r="AA8">
-        <v>0.07955915702811032</v>
+        <v>0.1063659215150332</v>
       </c>
       <c r="AB8">
-        <v>0.07619008609616612</v>
+        <v>0.06438462970745118</v>
       </c>
       <c r="AC8">
-        <v>0.003369070931944204</v>
+        <v>0.04198129180758201</v>
       </c>
       <c r="AD8">
-        <v>14.6</v>
+        <v>99.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>14.6</v>
+        <v>99.7</v>
       </c>
       <c r="AG8">
-        <v>14.6</v>
+        <v>50</v>
       </c>
       <c r="AH8">
-        <v>0.04138321995464853</v>
+        <v>0.1987243372533387</v>
       </c>
       <c r="AI8">
-        <v>0.07087378640776699</v>
+        <v>0.4401766004415011</v>
       </c>
       <c r="AJ8">
-        <v>0.04138321995464853</v>
+        <v>0.1106194690265487</v>
       </c>
       <c r="AK8">
-        <v>0.07087378640776699</v>
+        <v>0.2828054298642534</v>
       </c>
       <c r="AL8">
-        <v>0.951</v>
+        <v>1.53</v>
       </c>
       <c r="AM8">
-        <v>0.951</v>
+        <v>1.42</v>
       </c>
       <c r="AN8">
-        <v>0.5195729537366548</v>
+        <v>5.331550802139038</v>
       </c>
       <c r="AO8">
-        <v>29.44269190325973</v>
+        <v>11.96078431372549</v>
       </c>
       <c r="AP8">
-        <v>0.5195729537366548</v>
+        <v>2.67379679144385</v>
       </c>
       <c r="AQ8">
-        <v>29.44269190325973</v>
+        <v>12.88732394366197</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1511,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sievi Capital Plc (HLSE:SIEVI)</t>
+          <t>Lifeline SPAC I Oyj (HLSE:LL1SPAC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1504,122 +1519,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>-0.191</v>
-      </c>
-      <c r="E9">
-        <v>-0.24</v>
-      </c>
-      <c r="G9">
-        <v>3.776683087027915</v>
-      </c>
-      <c r="H9">
-        <v>3.776683087027915</v>
-      </c>
-      <c r="I9">
-        <v>0.2939244663382595</v>
-      </c>
-      <c r="J9">
-        <v>0.2939244663382595</v>
-      </c>
       <c r="K9">
-        <v>3.28</v>
-      </c>
-      <c r="L9">
-        <v>0.5385878489326765</v>
+        <v>-0.3</v>
       </c>
       <c r="M9">
-        <v>0.024</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.0003283173734610123</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.007317073170731708</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>0.024</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.0003283173734610123</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.007317073170731708</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>3.35</v>
+        <v>1.27</v>
       </c>
       <c r="V9">
-        <v>0.04582763337893297</v>
+        <v>0.009379615952732644</v>
       </c>
       <c r="W9">
-        <v>0.03215686274509804</v>
+        <v>-0.1006711409395973</v>
       </c>
       <c r="X9">
-        <v>0.08077946090680761</v>
+        <v>0.0823428380822596</v>
       </c>
       <c r="Y9">
-        <v>-0.04862259816170957</v>
+        <v>-0.1830139790218569</v>
       </c>
       <c r="Z9">
-        <v>0.06331482752167676</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>0.01860977689060778</v>
+        <v>-0.01103540926974378</v>
       </c>
       <c r="AB9">
-        <v>0.07658272410932017</v>
+        <v>0.06325274253652857</v>
       </c>
       <c r="AC9">
-        <v>-0.05797294721871239</v>
+        <v>-0.07428815180627235</v>
       </c>
       <c r="AD9">
-        <v>10.7</v>
+        <v>108.9</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>10.7</v>
+        <v>108.9</v>
       </c>
       <c r="AG9">
-        <v>7.35</v>
+        <v>107.63</v>
       </c>
       <c r="AH9">
-        <v>0.1276849642004773</v>
+        <v>0.4457634056487925</v>
       </c>
       <c r="AI9">
-        <v>0.1030828516377649</v>
+        <v>0.9748455823113419</v>
       </c>
       <c r="AJ9">
-        <v>0.09136109384711001</v>
+        <v>0.4428671357445583</v>
       </c>
       <c r="AK9">
-        <v>0.07317073170731708</v>
+        <v>0.9745563201738501</v>
       </c>
       <c r="AL9">
-        <v>0.12</v>
+        <v>1.1</v>
       </c>
       <c r="AM9">
-        <v>0.12</v>
-      </c>
-      <c r="AN9">
-        <v>5.911602209944751</v>
+        <v>-0.8499999999999999</v>
       </c>
       <c r="AO9">
-        <v>14.91666666666667</v>
-      </c>
-      <c r="AP9">
-        <v>4.060773480662983</v>
+        <v>-1.045454545454545</v>
       </c>
       <c r="AQ9">
-        <v>14.91666666666667</v>
+        <v>1.352941176470588</v>
       </c>
     </row>
     <row r="10">
@@ -1638,116 +1623,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D10">
+        <v>0.477</v>
+      </c>
       <c r="G10">
-        <v>0.1155015197568389</v>
+        <v>-0.05604938271604938</v>
       </c>
       <c r="H10">
-        <v>0.1155015197568389</v>
+        <v>-0.05604938271604938</v>
       </c>
       <c r="I10">
-        <v>-0.04214792299898683</v>
+        <v>-0.02493827160493827</v>
       </c>
       <c r="J10">
-        <v>-0.04214792299898683</v>
+        <v>-0.02493827160493827</v>
       </c>
       <c r="K10">
-        <v>-6.31</v>
+        <v>-18.1</v>
       </c>
       <c r="L10">
-        <v>-0.06393110435663626</v>
+        <v>-0.2234567901234568</v>
       </c>
       <c r="M10">
-        <v>3.02</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.1037800687285223</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>-0.4786053882725833</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>3.02</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.1037800687285223</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>-0.4786053882725833</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>9.17</v>
+        <v>7.43</v>
       </c>
       <c r="V10">
-        <v>0.3151202749140893</v>
+        <v>0.2846743295019157</v>
       </c>
       <c r="W10">
-        <v>-0.07602409638554217</v>
+        <v>-0.2823712948517941</v>
       </c>
       <c r="X10">
-        <v>0.1202856677436954</v>
+        <v>0.08600399885699968</v>
       </c>
       <c r="Y10">
-        <v>-0.1963097641292376</v>
+        <v>-0.3683752937087938</v>
       </c>
       <c r="Z10">
-        <v>1.17921146953405</v>
+        <v>1.083902047370534</v>
       </c>
       <c r="AA10">
-        <v>-0.04970131421744325</v>
+        <v>-0.02703064365047505</v>
       </c>
       <c r="AB10">
-        <v>0.07366975161655316</v>
+        <v>0.06532864642324035</v>
       </c>
       <c r="AC10">
-        <v>-0.1233710658339964</v>
+        <v>-0.09235929007371541</v>
       </c>
       <c r="AD10">
-        <v>42.5</v>
+        <v>25.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>42.5</v>
+        <v>25.5</v>
       </c>
       <c r="AG10">
-        <v>33.33</v>
+        <v>18.07</v>
       </c>
       <c r="AH10">
-        <v>0.5935754189944135</v>
+        <v>0.4941860465116279</v>
       </c>
       <c r="AI10">
-        <v>0.391705069124424</v>
+        <v>0.3355263157894737</v>
       </c>
       <c r="AJ10">
-        <v>0.5338779432964921</v>
+        <v>0.4091011999094408</v>
       </c>
       <c r="AK10">
-        <v>0.3355481727574751</v>
+        <v>0.2635263234650722</v>
       </c>
       <c r="AL10">
-        <v>4.67</v>
+        <v>13.4</v>
       </c>
       <c r="AM10">
-        <v>3.48</v>
+        <v>10.39</v>
       </c>
       <c r="AN10">
-        <v>12.61127596439169</v>
+        <v>5.279503105590062</v>
       </c>
       <c r="AO10">
-        <v>-0.8907922912205568</v>
+        <v>-0.1507462686567164</v>
       </c>
       <c r="AP10">
-        <v>9.890207715133529</v>
+        <v>3.74120082815735</v>
       </c>
       <c r="AQ10">
-        <v>-1.195402298850575</v>
+        <v>-0.1944177093358999</v>
       </c>
     </row>
     <row r="11">
@@ -1767,25 +1752,25 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.147</v>
+        <v>0.128</v>
       </c>
       <c r="G11">
-        <v>-4.365168539325843</v>
+        <v>-13.57575757575758</v>
       </c>
       <c r="H11">
-        <v>-4.365168539325843</v>
+        <v>-13.57575757575758</v>
       </c>
       <c r="I11">
-        <v>-4.471910112359551</v>
+        <v>-12.28787878787879</v>
       </c>
       <c r="J11">
-        <v>-4.471910112359551</v>
+        <v>-12.28787878787879</v>
       </c>
       <c r="K11">
-        <v>-0.547</v>
+        <v>-3.67</v>
       </c>
       <c r="L11">
-        <v>-3.073033707865169</v>
+        <v>-55.6060606060606</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1809,73 +1794,73 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0.278</v>
+        <v>0.099</v>
       </c>
       <c r="V11">
-        <v>0.03228803716608595</v>
+        <v>0.007443609022556391</v>
       </c>
       <c r="W11">
-        <v>-0.04972727272727273</v>
+        <v>-0.28671875</v>
       </c>
       <c r="X11">
-        <v>0.08786652349135464</v>
+        <v>0.07131930765400177</v>
       </c>
       <c r="Y11">
-        <v>-0.1375937962186274</v>
+        <v>-0.3580380576540018</v>
       </c>
       <c r="Z11">
-        <v>0.01164007324091028</v>
+        <v>0.004174045029091829</v>
       </c>
       <c r="AA11">
-        <v>-0.05205336123463249</v>
+        <v>-0.05129015937262839</v>
       </c>
       <c r="AB11">
-        <v>0.07682015113052301</v>
+        <v>0.06531014946774351</v>
       </c>
       <c r="AC11">
-        <v>-0.1288735123651555</v>
+        <v>-0.1166003088403719</v>
       </c>
       <c r="AD11">
-        <v>3.29</v>
+        <v>3.78</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>3.29</v>
+        <v>3.78</v>
       </c>
       <c r="AG11">
-        <v>3.012</v>
+        <v>3.681</v>
       </c>
       <c r="AH11">
-        <v>0.2764705882352941</v>
+        <v>0.221311475409836</v>
       </c>
       <c r="AI11">
-        <v>0.2044748290863891</v>
+        <v>0.220023282887078</v>
       </c>
       <c r="AJ11">
-        <v>0.2591636551368095</v>
+        <v>0.2167716860020022</v>
       </c>
       <c r="AK11">
-        <v>0.1904882367821907</v>
+        <v>0.2155026052338856</v>
       </c>
       <c r="AL11">
-        <v>0.414</v>
+        <v>1.08</v>
       </c>
       <c r="AM11">
-        <v>0.299</v>
+        <v>1.08</v>
       </c>
       <c r="AN11">
-        <v>-4.148802017654477</v>
+        <v>-4.660912453760789</v>
       </c>
       <c r="AO11">
-        <v>-1.922705314009662</v>
+        <v>-0.7509259259259259</v>
       </c>
       <c r="AP11">
-        <v>-3.798234552332913</v>
+        <v>-4.538840937114673</v>
       </c>
       <c r="AQ11">
-        <v>-2.662207357859532</v>
+        <v>-0.7509259259259259</v>
       </c>
     </row>
     <row r="12">
@@ -1886,7 +1871,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lifeline SPAC I Oyj (HLSE:LL1SPAC)</t>
+          <t>KH Group Oyj (HLSE:KHG)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1894,8 +1879,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.5489999999999999</v>
+      </c>
+      <c r="G12">
+        <v>-0.06199770378874857</v>
+      </c>
+      <c r="H12">
+        <v>-0.06199770378874857</v>
+      </c>
+      <c r="I12">
+        <v>-0.1360505166475316</v>
+      </c>
+      <c r="J12">
+        <v>-0.1360505166475316</v>
+      </c>
       <c r="K12">
-        <v>-19.6</v>
+        <v>-10.9</v>
+      </c>
+      <c r="L12">
+        <v>-0.06257175660160735</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1919,52 +1922,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1.97</v>
+        <v>20.5</v>
       </c>
       <c r="V12">
-        <v>0.014668652271035</v>
+        <v>0.3919694072657744</v>
+      </c>
+      <c r="W12">
+        <v>-0.0509822263797942</v>
       </c>
       <c r="X12">
-        <v>0.09948038104377877</v>
+        <v>0.1414876949908473</v>
+      </c>
+      <c r="Y12">
+        <v>-0.1924699213706415</v>
+      </c>
+      <c r="Z12">
+        <v>0.5794112755695991</v>
+      </c>
+      <c r="AA12">
+        <v>-0.07882920339264925</v>
       </c>
       <c r="AB12">
-        <v>0.0783933310665597</v>
+        <v>0.06171054052623557</v>
+      </c>
+      <c r="AC12">
+        <v>-0.1405397439188848</v>
       </c>
       <c r="AD12">
-        <v>103.2</v>
+        <v>188</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>103.2</v>
+        <v>188</v>
       </c>
       <c r="AG12">
-        <v>101.23</v>
+        <v>167.5</v>
       </c>
       <c r="AH12">
-        <v>0.4345263157894737</v>
+        <v>0.7823553890969621</v>
       </c>
       <c r="AI12">
-        <v>0.971934450932379</v>
+        <v>0.6868834490317867</v>
       </c>
       <c r="AJ12">
-        <v>0.4297966288795482</v>
+        <v>0.762056414922657</v>
       </c>
       <c r="AK12">
-        <v>0.9714038959792726</v>
+        <v>0.6615323854660348</v>
       </c>
       <c r="AL12">
-        <v>0.5620000000000001</v>
+        <v>5.98</v>
       </c>
       <c r="AM12">
-        <v>0.5620000000000001</v>
+        <v>5.239000000000001</v>
+      </c>
+      <c r="AN12">
+        <v>-24.93368700265252</v>
       </c>
       <c r="AO12">
-        <v>-33.98576512455516</v>
+        <v>-3.963210702341137</v>
+      </c>
+      <c r="AP12">
+        <v>-22.21485411140583</v>
       </c>
       <c r="AQ12">
-        <v>-33.98576512455516</v>
+        <v>-4.523764077113952</v>
       </c>
     </row>
   </sheetData>
